--- a/exposan/VFA/LCA data/impact_items.xlsx
+++ b/exposan/VFA/LCA data/impact_items.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blues/Documents/EXPOsan/exposan/VFA/LCA data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4B3C71-FD59-B34D-A54E-3434E0C2D48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07EC946-CAB6-1343-B9D7-1B83E1D69F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36060" yWindow="160" windowWidth="29400" windowHeight="16760" activeTab="1" xr2:uid="{BD97E243-0BB4-3F42-9EBC-00D49E7EE019}"/>
+    <workbookView xWindow="32520" yWindow="-1540" windowWidth="29400" windowHeight="16760" activeTab="1" xr2:uid="{BD97E243-0BB4-3F42-9EBC-00D49E7EE019}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="2" r:id="rId1"/>
